--- a/output/pdf_financials_xlsx/VLLC.xlsx
+++ b/output/pdf_financials_xlsx/VLLC.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.263776</v>
+        <v>0.556708</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.263776</v>
+        <v>-0.556708</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.318226</v>
       </c>
     </row>
     <row r="35">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.318226</v>
       </c>
     </row>
     <row r="37">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3144,11 +3144,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-0.556708</v>
+        <v>0.556708</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
